--- a/Modelo.xlsx
+++ b/Modelo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecrcampus-my.sharepoint.com/personal/carlos_perezc_ecr_edu_co/Documents/Backup ECR Tecnologia/Documents/GitHub/UserAutomationService/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C9E0AED7-873A-440E-8F77-81EDF55FEAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6CB11D5-AF80-460B-BC9B-F48C5181D8A6}"/>
+  <xr:revisionPtr revIDLastSave="439" documentId="8_{C9E0AED7-873A-440E-8F77-81EDF55FEAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FF2EE48-F826-47E4-A237-429A038FB102}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8356DB42-F3D4-4815-A35D-A3037C274E54}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Tipo de Solicitud</t>
   </si>
@@ -92,20 +92,29 @@
     <t>Correo Electrónico Personal</t>
   </si>
   <si>
-    <t>Reactivacion</t>
-  </si>
-  <si>
     <t xml:space="preserve">C.C </t>
   </si>
   <si>
+    <t xml:space="preserve">Creacion </t>
+  </si>
+  <si>
     <t>Estudiante</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO PEREZ </t>
+  </si>
+  <si>
+    <t>horrorotika@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +143,27 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -149,7 +179,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -161,16 +191,91 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -180,9 +285,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -192,36 +295,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -235,9 +319,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,29 +677,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99DEFBD-7003-4ADE-893F-21ED90C4A43E}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" customWidth="1"/>
+    <col min="3" max="3" width="21.6328125" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -618,20 +708,37 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="10">
+        <v>1032444793</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1">
@@ -649,6 +756,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>